--- a/scorecard.xlsx
+++ b/scorecard.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Requests" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Entities" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requests" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entities" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,36 +442,8 @@
   </sheetPr>
   <dimension ref="A1:Z281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="22" customWidth="1" min="17" max="17"/>
-    <col width="16" customWidth="1" min="18" max="18"/>
-    <col width="28" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
-    <col width="28" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="10" customWidth="1" min="24" max="24"/>
-    <col width="10" customWidth="1" min="25" max="25"/>
-    <col width="36" customWidth="1" min="26" max="26"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Request ID</t>
@@ -838,12 +810,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Awaiting Response</t>
+          <t>No Responsive Documents</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>processed</t>
+          <t>no_docs</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -884,17 +856,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2025-12-26 13:10</t>
+          <t>2026-06-02 19:19</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-26 13:10</t>
+          <t>2026-06-02 19:19</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>119</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -923,7 +895,9 @@
           <t>Bow School District/SAU67</t>
         </is>
       </c>
-      <c r="V4" s="3" t="n"/>
+      <c r="V4" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="W4" s="3" t="n"/>
       <c r="X4" s="3">
         <f>IF(Y4=TRUE,"",IF(ISNUMBER(W4),W4,V4))</f>
@@ -993,18 +967,18 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-05-14 05:00</t>
+          <t>2026-06-30 05:00</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>149</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1284,12 +1258,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>No Responsive Documents</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>no_docs</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1330,17 +1304,17 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2025-12-29 17:04</t>
+          <t>2026-06-15 13:09</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-29 17:04</t>
+          <t>2026-06-15 13:09</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>128</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1370,7 +1344,7 @@
         </is>
       </c>
       <c r="V8" s="3" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="W8" s="3" t="n"/>
       <c r="X8" s="3">
@@ -1395,12 +1369,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>No Responsive Documents</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>no_docs</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1481,7 +1455,7 @@
         </is>
       </c>
       <c r="V9" s="3" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="W9" s="3" t="n"/>
       <c r="X9" s="3">
@@ -1617,12 +1591,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Processing</t>
+          <t>Partially Completed</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1653,7 +1627,7 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.04</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1663,18 +1637,18 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-05-15 12:31</t>
+          <t>2026-06-03 21:18</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>43</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1684,7 +1658,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>transparent-nh</t>
+          <t>transparent-nh, nh-inperson</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
@@ -2281,12 +2255,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>No Responsive Documents</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>no_docs</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2367,7 +2341,7 @@
         </is>
       </c>
       <c r="V17" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W17" s="3" t="n"/>
       <c r="X17" s="3">
@@ -2503,12 +2477,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Awaiting Response</t>
+          <t>Partially Completed</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>processed</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2727,12 +2701,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>No Responsive Documents</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>no_docs</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2773,17 +2747,17 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2025-12-29 17:09</t>
+          <t>2026-05-29 19:08</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2025-12-29 17:09</t>
+          <t>2026-05-29 19:08</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>117</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
@@ -2813,7 +2787,7 @@
         </is>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="W21" s="3" t="n"/>
       <c r="X21" s="3">
@@ -2949,12 +2923,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Processing</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2995,20 +2969,20 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-05-15 12:31</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>2026-05-20 16:33</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2026-05-20 16:33</t>
+        </is>
+      </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>https://www.muckrock.com/foi/durham-3859/ai-chat-logs-town-of-durham-211333/</t>
@@ -3034,7 +3008,9 @@
           <t>Oyster River Cooperative School District/SAU5</t>
         </is>
       </c>
-      <c r="V23" s="3" t="n"/>
+      <c r="V23" s="3" t="n">
+        <v>-4</v>
+      </c>
       <c r="W23" s="3" t="n"/>
       <c r="X23" s="3">
         <f>IF(Y23=TRUE,"",IF(ISNUMBER(W23),W23,V23))</f>
@@ -3104,17 +3080,17 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-02-17 13:58</t>
+          <t>2026-05-21 20:01</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-02-17 13:58</t>
+          <t>2026-05-21 20:01</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>111</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
@@ -3544,18 +3520,18 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-05-14 05:00</t>
+          <t>2026-06-30 05:00</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>149</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3835,12 +3811,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>No Responsive Documents</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>no_docs</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3881,17 +3857,17 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-01-12 13:44</t>
+          <t>2026-06-15 16:09</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-01-12 13:44</t>
+          <t>2026-06-15 16:09</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>128</t>
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
@@ -3921,7 +3897,7 @@
         </is>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="W31" s="3" t="n"/>
       <c r="X31" s="3">
@@ -3946,12 +3922,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>No Responsive Documents</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>no_docs</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -4032,7 +4008,7 @@
         </is>
       </c>
       <c r="V32" s="3" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="W32" s="3" t="n"/>
       <c r="X32" s="3">
@@ -4168,12 +4144,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Processing</t>
+          <t>No Responsive Documents</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>no_docs</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -4214,20 +4190,20 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-05-15 12:32</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>2026-05-22 14:09</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:09</t>
+        </is>
+      </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr"/>
       <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>https://www.muckrock.com/foi/franklin-3874/ai-policy-franklin-clerk-211334/</t>
@@ -4253,7 +4229,9 @@
           <t>Franklin School District/SAU18</t>
         </is>
       </c>
-      <c r="V34" s="3" t="n"/>
+      <c r="V34" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="W34" s="3" t="n"/>
       <c r="X34" s="3">
         <f>IF(Y34=TRUE,"",IF(ISNUMBER(W34),W34,V34))</f>
@@ -5058,12 +5036,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Awaiting Acknowledgement</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ack</t>
+          <t>done</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -5091,7 +5069,11 @@
           <t>114503</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>RTK-2025-0000165</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>0</t>
@@ -5110,12 +5092,12 @@
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>149</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>88</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5144,7 +5126,7 @@
         </is>
       </c>
       <c r="V42" s="3" t="n">
-        <v>-5</v>
+        <v>3</v>
       </c>
       <c r="W42" s="3" t="n"/>
       <c r="X42" s="3">
@@ -5236,7 +5218,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>transparent-nh, nh-citizen, nh-inperson</t>
+          <t>transparent-nh, nh-citizen</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
@@ -5280,12 +5262,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>No Responsive Documents</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>no_docs</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -5366,7 +5348,7 @@
         </is>
       </c>
       <c r="V44" s="3" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="W44" s="3" t="n"/>
       <c r="X44" s="3">
@@ -5391,12 +5373,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Fix Required</t>
+          <t>Partially Completed</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>fix</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -5443,12 +5425,12 @@
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>149</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>119</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5483,7 +5465,7 @@
         <v/>
       </c>
       <c r="Y45" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z45" s="3" t="n"/>
     </row>
@@ -5500,12 +5482,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Processing</t>
+          <t>No Responsive Documents</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>no_docs</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -5546,20 +5528,20 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-05-15 12:32</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
+          <t>2026-05-20 16:29</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>2026-05-20 16:29</t>
+        </is>
+      </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr"/>
       <c r="Q46" s="2" t="inlineStr">
         <is>
           <t>https://www.muckrock.com/foi/durham-3859/ai-policy-town-of-durham-211335/</t>
@@ -5585,7 +5567,9 @@
           <t>Oyster River Cooperative School District/SAU5</t>
         </is>
       </c>
-      <c r="V46" s="3" t="n"/>
+      <c r="V46" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="W46" s="3" t="n"/>
       <c r="X46" s="3">
         <f>IF(Y46=TRUE,"",IF(ISNUMBER(W46),W46,V46))</f>
@@ -5609,12 +5593,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>No Responsive Documents</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>no_docs</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -5655,17 +5639,17 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-02-17 13:59</t>
+          <t>2026-05-21 20:01</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-02-17 13:59</t>
+          <t>2026-05-21 20:01</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>111</t>
         </is>
       </c>
       <c r="P47" t="inlineStr"/>
@@ -5691,7 +5675,7 @@
         </is>
       </c>
       <c r="V47" s="3" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="W47" s="3" t="n"/>
       <c r="X47" s="3">
@@ -5827,12 +5811,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Awaiting Acknowledgement</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ack</t>
+          <t>done</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5873,20 +5857,20 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-05-15 12:29</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
+          <t>2026-05-15 18:59</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>2026-05-15 18:59</t>
+        </is>
+      </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr"/>
       <c r="Q49" s="2" t="inlineStr">
         <is>
           <t>https://www.muckrock.com/foi/salem-3985/ethics-and-conflict-of-interest-rules-211331/</t>
@@ -5912,7 +5896,9 @@
           <t>Salem School District/SAU57</t>
         </is>
       </c>
-      <c r="V49" s="3" t="n"/>
+      <c r="V49" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="W49" s="3" t="n"/>
       <c r="X49" s="3">
         <f>IF(Y49=TRUE,"",IF(ISNUMBER(W49),W49,V49))</f>
@@ -5982,17 +5968,17 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-02-17 14:06</t>
+          <t>2026-05-21 20:01</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2026-02-17 14:06</t>
+          <t>2026-05-21 20:01</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>93</t>
         </is>
       </c>
       <c r="P50" t="inlineStr"/>
@@ -6047,12 +6033,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Fix Required</t>
+          <t>Partially Completed</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>fix</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -6099,12 +6085,12 @@
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>131</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>98</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6114,7 +6100,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>transparent-nh</t>
+          <t>transparent-nh, nh-inperson</t>
         </is>
       </c>
       <c r="S51" s="3" t="inlineStr">
@@ -6139,7 +6125,7 @@
         <v/>
       </c>
       <c r="Y51" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z51" s="3" t="n"/>
     </row>
@@ -6757,7 +6743,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-04-13 05:00</t>
+          <t>2026-07-01 05:00</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -7224,7 +7210,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>transparent-nh, nh-inperson</t>
+          <t>transparent-nh</t>
         </is>
       </c>
       <c r="S61" s="3" t="inlineStr">
@@ -7243,7 +7229,7 @@
         </is>
       </c>
       <c r="V61" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W61" s="3" t="n"/>
       <c r="X61" s="3">
@@ -7379,12 +7365,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Processing</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>done</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -7425,20 +7411,20 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2026-05-14 21:28</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
+          <t>2026-05-15 12:48</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>2026-05-15 12:48</t>
+        </is>
+      </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr"/>
       <c r="Q63" s="2" t="inlineStr">
         <is>
           <t>https://www.muckrock.com/foi/berlin-3819/ethics-and-conflict-of-interest-rules-berlin-clerk-211278/</t>
@@ -7464,7 +7450,9 @@
           <t>Berlin School District/SAU 3</t>
         </is>
       </c>
-      <c r="V63" s="3" t="n"/>
+      <c r="V63" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="W63" s="3" t="n"/>
       <c r="X63" s="3">
         <f>IF(Y63=TRUE,"",IF(ISNUMBER(W63),W63,V63))</f>
@@ -7534,18 +7522,18 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2026-04-07 05:00</t>
+          <t>2026-07-07 05:00</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>153</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7714,12 +7702,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Processing</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>done</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -7760,20 +7748,20 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2026-05-14 21:28</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
+          <t>2026-05-22 20:48</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>2026-05-22 20:48</t>
+        </is>
+      </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr"/>
       <c r="Q66" s="2" t="inlineStr">
         <is>
           <t>https://www.muckrock.com/foi/claremont-3840/ethics-and-conflict-of-interest-rules-claremont-clerk-211277/</t>
@@ -7799,7 +7787,9 @@
           <t>Claremont School District/SAU6</t>
         </is>
       </c>
-      <c r="V66" s="3" t="n"/>
+      <c r="V66" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="W66" s="3" t="n"/>
       <c r="X66" s="3">
         <f>IF(Y66=TRUE,"",IF(ISNUMBER(W66),W66,V66))</f>
@@ -8045,12 +8035,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Processing</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>done</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -8091,20 +8081,20 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2026-05-14 21:28</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
+          <t>2026-05-15 13:37</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>2026-05-15 13:37</t>
+        </is>
+      </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr"/>
       <c r="Q69" s="2" t="inlineStr">
         <is>
           <t>https://www.muckrock.com/foi/rochester-3980/ethics-and-conflict-of-interest-rules-rochester-clerk-211275/</t>
@@ -8130,7 +8120,9 @@
           <t>Rochester School District/SAU54</t>
         </is>
       </c>
-      <c r="V69" s="3" t="n"/>
+      <c r="V69" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="W69" s="3" t="n"/>
       <c r="X69" s="3">
         <f>IF(Y69=TRUE,"",IF(ISNUMBER(W69),W69,V69))</f>
@@ -8154,12 +8146,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Processing</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>done</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -8200,20 +8192,20 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2026-05-14 21:28</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
+          <t>2026-05-15 17:54</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>2026-05-15 17:54</t>
+        </is>
+      </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr"/>
       <c r="Q70" s="2" t="inlineStr">
         <is>
           <t>https://www.muckrock.com/foi/durham-3859/ethics-and-conflict-of-interest-rules-town-of-durham-211276/</t>
@@ -8239,7 +8231,9 @@
           <t>Oyster River Cooperative School District/SAU5</t>
         </is>
       </c>
-      <c r="V70" s="3" t="n"/>
+      <c r="V70" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="W70" s="3" t="n"/>
       <c r="X70" s="3">
         <f>IF(Y70=TRUE,"",IF(ISNUMBER(W70),W70,V70))</f>
@@ -8330,7 +8324,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>transparent-nh, nh-in-person</t>
+          <t>transparent-nh, nh-inperson</t>
         </is>
       </c>
       <c r="S71" s="3" t="inlineStr">
@@ -8485,12 +8479,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Awaiting Acknowledgement</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ack</t>
+          <t>done</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -8531,20 +8525,20 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2026-05-04 05:02</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
+          <t>2026-06-11 17:31</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>2026-06-11 17:31</t>
+        </is>
+      </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr"/>
       <c r="Q73" s="2" t="inlineStr">
         <is>
           <t>https://www.muckrock.com/foi/bow-3822/highest-value-rfps-bow-clerk-200671/</t>
@@ -8571,7 +8565,7 @@
         </is>
       </c>
       <c r="V73" s="3" t="n">
-        <v>-5</v>
+        <v>3</v>
       </c>
       <c r="W73" s="3" t="n"/>
       <c r="X73" s="3">
@@ -8753,18 +8747,18 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2026-05-04 05:02</t>
+          <t>2026-07-03 05:03</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>146</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -8868,18 +8862,18 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2026-05-13 05:01</t>
+          <t>2026-07-14 05:00</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>146</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -8933,12 +8927,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Partially Completed</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -8979,7 +8973,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2025-12-29 17:02</t>
+          <t>2026-06-15 16:16</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -9018,9 +9012,7 @@
           <t>Claremont School District/SAU6</t>
         </is>
       </c>
-      <c r="V77" s="3" t="n">
-        <v>-4</v>
-      </c>
+      <c r="V77" s="3" t="n"/>
       <c r="W77" s="3" t="n"/>
       <c r="X77" s="3">
         <f>IF(Y77=TRUE,"",IF(ISNUMBER(W77),W77,V77))</f>
@@ -9266,12 +9258,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Processing</t>
+          <t>Fix Required</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>fix</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -9302,7 +9294,7 @@
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -9312,18 +9304,18 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2026-05-14 21:30</t>
+          <t>2026-06-26 16:40</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>44</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9358,7 +9350,7 @@
         <v/>
       </c>
       <c r="Y80" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z80" s="3" t="n"/>
     </row>
@@ -9597,12 +9589,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Fix Required</t>
+          <t>Partially Completed</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>fix</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -9643,20 +9635,20 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2025-12-31 16:21</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
+          <t>2026-06-22 14:09</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>2026-06-22 14:09</t>
+        </is>
+      </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr"/>
       <c r="Q83" s="2" t="inlineStr">
         <is>
           <t>https://www.muckrock.com/foi/hopkinton-3905/highest-value-rfps-hopkinton-clerk-200670/</t>
@@ -9664,7 +9656,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>transparent-nh</t>
+          <t>transparent-nh, nh-inperson</t>
         </is>
       </c>
       <c r="S83" s="3" t="inlineStr">
@@ -9689,7 +9681,7 @@
         <v/>
       </c>
       <c r="Y83" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z83" s="3" t="n"/>
     </row>
@@ -9884,7 +9876,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>transparent-nh</t>
+          <t>transparent-nh, nh-inperson</t>
         </is>
       </c>
       <c r="S85" s="3" t="inlineStr">
@@ -9959,7 +9951,11 @@
           <t>114503</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr"/>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>26-356</t>
+        </is>
+      </c>
       <c r="K86" t="inlineStr">
         <is>
           <t>0</t>
@@ -9972,18 +9968,18 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2025-12-24 18:45</t>
+          <t>2026-05-20 17:25</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>146</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>40</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10087,12 +10083,12 @@
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>146</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>136</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -10211,7 +10207,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>transparent-nh</t>
+          <t>transparent-nh, nh-inperson</t>
         </is>
       </c>
       <c r="S88" s="3" t="inlineStr">
@@ -10230,7 +10226,7 @@
         </is>
       </c>
       <c r="V88" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="W88" s="3" t="n"/>
       <c r="X88" s="3">
@@ -10255,12 +10251,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Fix Required</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>fix</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -10304,17 +10300,17 @@
           <t>2026-02-11 16:11</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>2026-02-11 16:11</t>
+        </is>
+      </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr"/>
       <c r="Q89" s="2" t="inlineStr">
         <is>
           <t>https://www.muckrock.com/foi/rochester-3980/highest-value-rfps-rochester-clerk-200689/</t>
@@ -10322,7 +10318,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>transparent-nh, nh-citizen</t>
+          <t>transparent-nh, nh-citizen, nh-inperson</t>
         </is>
       </c>
       <c r="S89" s="3" t="inlineStr">
@@ -10340,14 +10336,16 @@
           <t>Rochester School District/SAU54</t>
         </is>
       </c>
-      <c r="V89" s="3" t="n"/>
+      <c r="V89" s="3" t="n">
+        <v>-4</v>
+      </c>
       <c r="W89" s="3" t="n"/>
       <c r="X89" s="3">
         <f>IF(Y89=TRUE,"",IF(ISNUMBER(W89),W89,V89))</f>
         <v/>
       </c>
       <c r="Y89" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z89" s="3" t="n"/>
     </row>
@@ -10364,12 +10362,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>done</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -10450,7 +10448,7 @@
         </is>
       </c>
       <c r="V90" s="3" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
       <c r="W90" s="3" t="n"/>
       <c r="X90" s="3">
@@ -10527,12 +10525,12 @@
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>146</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>119</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -10584,12 +10582,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Processing</t>
+          <t>Awaiting Response</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>processed</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -10630,18 +10628,18 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2026-05-14 21:30</t>
+          <t>2026-05-19 22:45</t>
         </is>
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>44</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>41</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -10669,7 +10667,9 @@
           <t>Oyster River Cooperative School District/SAU5</t>
         </is>
       </c>
-      <c r="V92" s="3" t="n"/>
+      <c r="V92" s="3" t="n">
+        <v>-3</v>
+      </c>
       <c r="W92" s="3" t="n"/>
       <c r="X92" s="3">
         <f>IF(Y92=TRUE,"",IF(ISNUMBER(W92),W92,V92))</f>
@@ -10693,12 +10693,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Awaiting Acknowledgement</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ack</t>
+          <t>done</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -10739,20 +10739,20 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2026-05-04 05:02</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
+          <t>2026-05-21 19:54</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>2026-05-21 19:54</t>
+        </is>
+      </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr"/>
       <c r="Q93" s="2" t="inlineStr">
         <is>
           <t>https://www.muckrock.com/foi/troy-4012/highest-value-rfps-troy-clerk-200680/</t>
@@ -10775,7 +10775,7 @@
         </is>
       </c>
       <c r="V93" s="3" t="n">
-        <v>-5</v>
+        <v>3</v>
       </c>
       <c r="W93" s="3" t="n"/>
       <c r="X93" s="3">
@@ -10800,12 +10800,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Processing</t>
+          <t>No Responsive Documents</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>no_docs</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -10846,20 +10846,20 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>2026-05-14 21:40</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
+          <t>2026-05-20 15:41</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>2026-05-20 15:41</t>
+        </is>
+      </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr"/>
       <c r="Q94" s="2" t="inlineStr">
         <is>
           <t>https://www.muckrock.com/foi/durham-3859/leadership-and-constituent-emails-211282/</t>
@@ -10885,7 +10885,9 @@
           <t>Oyster River Cooperative School District/SAU5</t>
         </is>
       </c>
-      <c r="V94" s="3" t="n"/>
+      <c r="V94" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="W94" s="3" t="n"/>
       <c r="X94" s="3">
         <f>IF(Y94=TRUE,"",IF(ISNUMBER(W94),W94,V94))</f>
@@ -10909,12 +10911,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Awaiting Acknowledgement</t>
+          <t>Awaiting Response</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>ack</t>
+          <t>processed</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -10945,7 +10947,7 @@
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>400</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -10955,18 +10957,18 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>2026-05-15 19:31</t>
+          <t>2026-07-01 13:25</t>
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>43</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -10994,7 +10996,9 @@
           <t>Monadnock Regional School District/SAU93</t>
         </is>
       </c>
-      <c r="V95" s="3" t="n"/>
+      <c r="V95" s="3" t="n">
+        <v>-3</v>
+      </c>
       <c r="W95" s="3" t="n"/>
       <c r="X95" s="3">
         <f>IF(Y95=TRUE,"",IF(ISNUMBER(W95),W95,V95))</f>
@@ -11018,12 +11022,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Awaiting Response</t>
+          <t>Partially Completed</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>processed</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -11070,12 +11074,12 @@
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>84</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>82</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -11103,9 +11107,7 @@
           <t>Shaker Regional School District/SAU80</t>
         </is>
       </c>
-      <c r="V96" s="3" t="n">
-        <v>-3</v>
-      </c>
+      <c r="V96" s="3" t="n"/>
       <c r="W96" s="3" t="n"/>
       <c r="X96" s="3">
         <f>IF(Y96=TRUE,"",IF(ISNUMBER(W96),W96,V96))</f>
@@ -11240,12 +11242,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Awaiting Response</t>
+          <t>Partially Completed</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>processed</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -11292,12 +11294,12 @@
       <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>84</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>72</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -11325,9 +11327,7 @@
           <t>Berlin</t>
         </is>
       </c>
-      <c r="V98" s="3" t="n">
-        <v>-3</v>
-      </c>
+      <c r="V98" s="3" t="n"/>
       <c r="W98" s="3" t="n"/>
       <c r="X98" s="3">
         <f>IF(Y98=TRUE,"",IF(ISNUMBER(W98),W98,V98))</f>
@@ -11351,12 +11351,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Awaiting Response</t>
+          <t>Partially Completed</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>processed</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -11397,7 +11397,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>2026-03-26 16:57</t>
+          <t>2026-06-02 17:27</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -11418,7 +11418,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>transparent-nh</t>
+          <t>transparent-nh, nh-inperson</t>
         </is>
       </c>
       <c r="S99" s="3" t="inlineStr">
@@ -11460,12 +11460,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Partially Completed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>done</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -11506,20 +11506,20 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>2026-03-27 20:13</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
+          <t>2026-06-01 20:12</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>2026-06-01 20:12</t>
+        </is>
+      </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="P100" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr"/>
       <c r="Q100" s="2" t="inlineStr">
         <is>
           <t>https://www.muckrock.com/foi/lebanon-3917/leadership-and-constituent-emails-city-clerk-207034/</t>
@@ -11545,7 +11545,9 @@
           <t>Lebanon School District/SAU88</t>
         </is>
       </c>
-      <c r="V100" s="3" t="n"/>
+      <c r="V100" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="W100" s="3" t="n"/>
       <c r="X100" s="3">
         <f>IF(Y100=TRUE,"",IF(ISNUMBER(W100),W100,V100))</f>
@@ -11621,12 +11623,12 @@
       <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>84</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>68</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -11680,12 +11682,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Awaiting Response</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>processed</t>
+          <t>done</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -11730,20 +11732,20 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>2026-04-06 14:14</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
+          <t>2026-07-01 15:20</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>2026-07-01 15:20</t>
+        </is>
+      </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="P102" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr"/>
       <c r="Q102" s="2" t="inlineStr">
         <is>
           <t>https://www.muckrock.com/foi/keene-3910/leadership-and-constituent-emails-city-clerks-office-207036/</t>
@@ -11770,7 +11772,7 @@
         </is>
       </c>
       <c r="V102" s="3" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="W102" s="3" t="n"/>
       <c r="X102" s="3">
@@ -11795,12 +11797,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Partially Completed</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -11862,7 +11864,7 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>transparent-nh</t>
+          <t>transparent-nh, nh-inperson</t>
         </is>
       </c>
       <c r="S103" s="3" t="inlineStr">
@@ -11880,9 +11882,7 @@
           <t>Claremont School District/SAU6</t>
         </is>
       </c>
-      <c r="V103" s="3" t="n">
-        <v>-4</v>
-      </c>
+      <c r="V103" s="3" t="n"/>
       <c r="W103" s="3" t="n"/>
       <c r="X103" s="3">
         <f>IF(Y103=TRUE,"",IF(ISNUMBER(W103),W103,V103))</f>
@@ -11952,7 +11952,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>2026-05-04 17:43</t>
+          <t>2026-06-16 13:42</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -11973,7 +11973,7 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>transparent-nh</t>
+          <t>transparent-nh, nh-inperson</t>
         </is>
       </c>
       <c r="S104" s="3" t="inlineStr">
@@ -12178,12 +12178,12 @@
       <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>84</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>47</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -12283,18 +12283,18 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>2026-03-30 12:36</t>
+          <t>2026-05-29 18:28</t>
         </is>
       </c>
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>84</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>33</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -12348,12 +12348,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Awaiting Response</t>
+          <t>Partially Completed</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>processed</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -12400,12 +12400,12 @@
       <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>84</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>69</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -12415,7 +12415,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>transparent-nh</t>
+          <t>transparent-nh, nh-inperson</t>
         </is>
       </c>
       <c r="S108" s="3" t="inlineStr">
@@ -12433,9 +12433,7 @@
           <t>Derry</t>
         </is>
       </c>
-      <c r="V108" s="3" t="n">
-        <v>-3</v>
-      </c>
+      <c r="V108" s="3" t="n"/>
       <c r="W108" s="3" t="n"/>
       <c r="X108" s="3">
         <f>IF(Y108=TRUE,"",IF(ISNUMBER(W108),W108,V108))</f>
@@ -12459,12 +12457,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Awaiting Response</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>processed</t>
+          <t>done</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -12505,17 +12503,17 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>2026-05-12 14:00</t>
+          <t>2026-06-01 16:08</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>2026-04-06 20:16</t>
+          <t>2026-06-01 16:08</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>53</t>
         </is>
       </c>
       <c r="P109" t="inlineStr"/>
@@ -12544,7 +12542,9 @@
           <t>Dover</t>
         </is>
       </c>
-      <c r="V109" s="3" t="n"/>
+      <c r="V109" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="W109" s="3" t="n"/>
       <c r="X109" s="3">
         <f>IF(Y109=TRUE,"",IF(ISNUMBER(W109),W109,V109))</f>
@@ -12568,12 +12568,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Awaiting Response</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>processed</t>
+          <t>done</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -12614,20 +12614,20 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>2026-05-06 09:19</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr"/>
+          <t>2026-05-19 19:47</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>2026-05-19 19:47</t>
+        </is>
+      </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="P110" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr"/>
       <c r="Q110" s="2" t="inlineStr">
         <is>
           <t>https://www.muckrock.com/foi/franklin-3874/leadership-and-constituent-emails-franklin-clerk-207037/</t>
@@ -12635,7 +12635,7 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>transparent-nh</t>
+          <t>transparent-nh, nh-inperson, nh-pickedup</t>
         </is>
       </c>
       <c r="S110" s="3" t="inlineStr">
@@ -12654,7 +12654,7 @@
         </is>
       </c>
       <c r="V110" s="3" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="W110" s="3" t="n"/>
       <c r="X110" s="3">
@@ -12836,18 +12836,18 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>2026-04-10 05:01</t>
+          <t>2026-07-01 05:00</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>84</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -12901,12 +12901,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Partially Completed</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -12986,9 +12986,7 @@
           <t>Interstate School District/SAU70</t>
         </is>
       </c>
-      <c r="V113" s="3" t="n">
-        <v>2</v>
-      </c>
+      <c r="V113" s="3" t="n"/>
       <c r="W113" s="3" t="n"/>
       <c r="X113" s="3">
         <f>IF(Y113=TRUE,"",IF(ISNUMBER(W113),W113,V113))</f>
@@ -13012,12 +13010,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Partially Completed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>done</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -13061,17 +13059,17 @@
           <t>2026-03-24 20:58</t>
         </is>
       </c>
-      <c r="N114" t="inlineStr"/>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>2026-03-24 20:58</t>
+        </is>
+      </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="P114" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr"/>
       <c r="Q114" s="2" t="inlineStr">
         <is>
           <t>https://www.muckrock.com/foi/hopkinton-3905/leadership-and-constituent-emails-hopkinton-clerk-207026/</t>
@@ -13079,7 +13077,7 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>transparent-nh</t>
+          <t>transparent-nh, nh-inperson</t>
         </is>
       </c>
       <c r="S114" s="3" t="inlineStr">
@@ -13097,7 +13095,9 @@
           <t>Hopkinton School District/SAU66</t>
         </is>
       </c>
-      <c r="V114" s="3" t="n"/>
+      <c r="V114" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="W114" s="3" t="n"/>
       <c r="X114" s="3">
         <f>IF(Y114=TRUE,"",IF(ISNUMBER(W114),W114,V114))</f>
@@ -13288,12 +13288,12 @@
       <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>84</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>68</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -13347,12 +13347,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>done</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -13393,17 +13393,17 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>2026-03-25 17:30</t>
+          <t>2026-05-21 15:35</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>2026-03-25 17:30</t>
+          <t>2026-05-21 15:35</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>46</t>
         </is>
       </c>
       <c r="P117" t="inlineStr"/>
@@ -13433,7 +13433,7 @@
         </is>
       </c>
       <c r="V117" s="3" t="n">
-        <v>-4</v>
+        <v>4</v>
       </c>
       <c r="W117" s="3" t="n"/>
       <c r="X117" s="3">
@@ -13680,12 +13680,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Awaiting Response</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>processed</t>
+          <t>done</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -13726,20 +13726,20 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>2026-05-11 08:32</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr"/>
+          <t>2026-05-29 06:00</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>2026-05-29 06:00</t>
+        </is>
+      </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="P120" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr"/>
       <c r="Q120" s="2" t="inlineStr">
         <is>
           <t>https://www.muckrock.com/foi/manchester-3931/leadership-and-constituent-emails-manchester-city-clerk-207046/</t>
@@ -13766,7 +13766,7 @@
         </is>
       </c>
       <c r="V120" s="3" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="W120" s="3" t="n"/>
       <c r="X120" s="3">
@@ -13791,12 +13791,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Awaiting Response</t>
+          <t>Fix Required</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>processed</t>
+          <t>fix</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -13827,7 +13827,7 @@
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>855</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -13837,13 +13837,13 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>2026-05-12 14:02</t>
+          <t>2026-07-08 15:49</t>
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>84</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -13876,16 +13876,14 @@
           <t>Manchester</t>
         </is>
       </c>
-      <c r="V121" s="3" t="n">
-        <v>-3</v>
-      </c>
+      <c r="V121" s="3" t="n"/>
       <c r="W121" s="3" t="n"/>
       <c r="X121" s="3">
         <f>IF(Y121=TRUE,"",IF(ISNUMBER(W121),W121,V121))</f>
         <v/>
       </c>
       <c r="Y121" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z121" s="3" t="n"/>
     </row>
@@ -14400,18 +14398,18 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>2026-04-09 19:58</t>
+          <t>2026-05-28 20:30</t>
         </is>
       </c>
       <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>84</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -14463,12 +14461,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Awaiting Acknowledgement</t>
+          <t>Consolidated</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>ack</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -14515,12 +14513,12 @@
       <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>84</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>68</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -14548,9 +14546,7 @@
           <t>Portsmouth School District/SAU52</t>
         </is>
       </c>
-      <c r="V127" s="3" t="n">
-        <v>-5</v>
-      </c>
+      <c r="V127" s="3" t="n"/>
       <c r="W127" s="3" t="n"/>
       <c r="X127" s="3">
         <f>IF(Y127=TRUE,"",IF(ISNUMBER(W127),W127,V127))</f>
@@ -14574,12 +14570,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Awaiting Response</t>
+          <t>Consolidated</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>processed</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -14626,12 +14622,12 @@
       <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>84</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>68</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
@@ -14641,7 +14637,7 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>transparent-nh</t>
+          <t>transparent-nh, nh-inperson</t>
         </is>
       </c>
       <c r="S128" s="3" t="inlineStr">
@@ -14659,9 +14655,7 @@
           <t>Portsmouth</t>
         </is>
       </c>
-      <c r="V128" s="3" t="n">
-        <v>-3</v>
-      </c>
+      <c r="V128" s="3" t="n"/>
       <c r="W128" s="3" t="n"/>
       <c r="X128" s="3">
         <f>IF(Y128=TRUE,"",IF(ISNUMBER(W128),W128,V128))</f>
@@ -14731,7 +14725,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>2026-04-08 17:14</t>
+          <t>2026-05-27 11:44</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -14794,12 +14788,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Awaiting Response</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>processed</t>
+          <t>done</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -14840,20 +14834,20 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>2026-04-22 18:28</t>
-        </is>
-      </c>
-      <c r="N130" t="inlineStr"/>
+          <t>2026-06-18 16:55</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>2026-06-18 16:55</t>
+        </is>
+      </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="P130" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr"/>
       <c r="Q130" s="2" t="inlineStr">
         <is>
           <t>https://www.muckrock.com/foi/rochester-3980/leadership-and-constituent-emails-rochester-school-district-207067/</t>
@@ -14880,7 +14874,7 @@
         </is>
       </c>
       <c r="V130" s="3" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="W130" s="3" t="n"/>
       <c r="X130" s="3">
@@ -15016,12 +15010,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Awaiting Response</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>processed</t>
+          <t>done</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -15062,20 +15056,20 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>2026-03-26 21:44</t>
-        </is>
-      </c>
-      <c r="N132" t="inlineStr"/>
+          <t>2026-05-29 20:52</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:59</t>
+        </is>
+      </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="P132" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr"/>
       <c r="Q132" s="2" t="inlineStr">
         <is>
           <t>https://www.muckrock.com/foi/salem-3985/leadership-and-constituent-emails-salem-school-districtsau57-207063/</t>
@@ -15102,7 +15096,7 @@
         </is>
       </c>
       <c r="V132" s="3" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="W132" s="3" t="n"/>
       <c r="X132" s="3">
@@ -15179,12 +15173,12 @@
       <c r="N133" t="inlineStr"/>
       <c r="O133" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>84</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>68</t>
         </is>
       </c>
       <c r="Q133" s="2" t="inlineStr">
@@ -15284,18 +15278,18 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>2026-04-07 05:00</t>
+          <t>2026-07-08 14:39</t>
         </is>
       </c>
       <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>84</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Q134" s="2" t="inlineStr">
@@ -15395,18 +15389,18 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>2026-04-16 11:38</t>
+          <t>2026-05-15 19:24</t>
         </is>
       </c>
       <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
           <t>43</t>
-        </is>
-      </c>
-      <c r="P135" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -15623,12 +15617,12 @@
       <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>84</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>82</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
@@ -15726,7 +15720,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>2026-04-06 14:46</t>
+          <t>2026-05-27 10:26</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -15835,18 +15829,18 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>2026-04-11 11:09</t>
+          <t>2026-05-26 14:25</t>
         </is>
       </c>
       <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>84</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>36</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
@@ -17837,18 +17831,18 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>2026-05-01 05:00</t>
+          <t>2026-07-02 05:01</t>
         </is>
       </c>
       <c r="N157" t="inlineStr"/>
       <c r="O157" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>113</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -18901,12 +18895,12 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Awaiting Acknowledgement</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>ack</t>
+          <t>done</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -18950,17 +18944,17 @@
           <t>2026-03-30 05:01</t>
         </is>
       </c>
-      <c r="N167" t="inlineStr"/>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>2026-03-30 05:01</t>
+        </is>
+      </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="P167" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr"/>
       <c r="Q167" s="2" t="inlineStr">
         <is>
           <t>https://www.muckrock.com/foi/dover-3855/parental-objections-dover-school-districtsau11-204171/</t>
@@ -18987,7 +18981,7 @@
         </is>
       </c>
       <c r="V167" s="3" t="n">
-        <v>-5</v>
+        <v>4</v>
       </c>
       <c r="W167" s="3" t="n"/>
       <c r="X167" s="3">
@@ -19290,12 +19284,12 @@
       <c r="N170" t="inlineStr"/>
       <c r="O170" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>115</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>77</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -20023,12 +20017,12 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Awaiting Response</t>
+          <t>No Responsive Documents</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>processed</t>
+          <t>no_docs</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -20069,20 +20063,20 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>2026-02-26 06:01</t>
-        </is>
-      </c>
-      <c r="N177" t="inlineStr"/>
+          <t>2026-05-26 14:20</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:20</t>
+        </is>
+      </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="P177" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr"/>
       <c r="Q177" s="2" t="inlineStr">
         <is>
           <t>https://www.muckrock.com/foi/new-hampshire-81/parental-objections-portsmouth-school-district-204179/</t>
@@ -20109,7 +20103,7 @@
         </is>
       </c>
       <c r="V177" s="3" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="W177" s="3" t="n"/>
       <c r="X177" s="3">
@@ -20408,12 +20402,12 @@
       <c r="N180" t="inlineStr"/>
       <c r="O180" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>115</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>77</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -20800,12 +20794,12 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Partially Completed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>done</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -20849,17 +20843,17 @@
           <t>2026-02-17 20:10</t>
         </is>
       </c>
-      <c r="N184" t="inlineStr"/>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>2026-02-17 20:10</t>
+        </is>
+      </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="P184" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr"/>
       <c r="Q184" s="2" t="inlineStr">
         <is>
           <t>https://www.muckrock.com/foi/belmont-3816/parental-objections-shaker-regional-school-districtsau80-204167/</t>
@@ -20867,7 +20861,7 @@
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>transparent-nh, nh-inperson</t>
+          <t>transparent-nh, nh-inperson, nh-pickedup</t>
         </is>
       </c>
       <c r="S184" s="3" t="inlineStr">
@@ -20885,7 +20879,9 @@
           <t>Belmont</t>
         </is>
       </c>
-      <c r="V184" s="3" t="n"/>
+      <c r="V184" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="W184" s="3" t="n"/>
       <c r="X184" s="3">
         <f>IF(Y184=TRUE,"",IF(ISNUMBER(W184),W184,V184))</f>
@@ -21242,12 +21238,12 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Awaiting Response</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>processed</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -21295,17 +21291,17 @@
           <t>2026-02-17 14:52</t>
         </is>
       </c>
-      <c r="N188" t="inlineStr"/>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>2026-02-17 14:52</t>
+        </is>
+      </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="P188" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr"/>
       <c r="Q188" s="2" t="inlineStr">
         <is>
           <t>https://www.muckrock.com/foi/portsmouth-3975/pd-chief-performance-evaluation-201884/</t>
@@ -21332,7 +21328,7 @@
         </is>
       </c>
       <c r="V188" s="3" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="W188" s="3" t="n"/>
       <c r="X188" s="3">
@@ -21357,12 +21353,12 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Awaiting Response</t>
+          <t>No Responsive Documents</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>processed</t>
+          <t>no_docs</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -21403,20 +21399,20 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>2026-03-24 11:36</t>
-        </is>
-      </c>
-      <c r="N189" t="inlineStr"/>
+          <t>2026-05-20 19:21</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>2026-05-20 19:21</t>
+        </is>
+      </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="P189" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr"/>
       <c r="Q189" s="2" t="inlineStr">
         <is>
           <t>https://www.muckrock.com/foi/salem-3985/pd-chief-performance-evaluation-201886/</t>
@@ -21443,7 +21439,7 @@
         </is>
       </c>
       <c r="V189" s="3" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="W189" s="3" t="n"/>
       <c r="X189" s="3">
@@ -21514,18 +21510,18 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>2026-05-15 19:35</t>
+          <t>2026-07-08 05:00</t>
         </is>
       </c>
       <c r="N190" t="inlineStr"/>
       <c r="O190" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>43</t>
         </is>
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
@@ -21553,7 +21549,9 @@
           <t>Monadnock Regional School District/SAU93</t>
         </is>
       </c>
-      <c r="V190" s="3" t="n"/>
+      <c r="V190" s="3" t="n">
+        <v>-5</v>
+      </c>
       <c r="W190" s="3" t="n"/>
       <c r="X190" s="3">
         <f>IF(Y190=TRUE,"",IF(ISNUMBER(W190),W190,V190))</f>
@@ -21688,12 +21686,12 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Awaiting Acknowledgement</t>
+          <t>Partially Completed</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>ack</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -21734,18 +21732,18 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>2026-05-12 17:20</t>
+          <t>2026-05-15 18:24</t>
         </is>
       </c>
       <c r="N192" t="inlineStr"/>
       <c r="O192" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>153</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>43</t>
         </is>
       </c>
       <c r="Q192" s="2" t="inlineStr">
@@ -21755,7 +21753,7 @@
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>transparent-nh</t>
+          <t>transparent-nh, nh-inperson</t>
         </is>
       </c>
       <c r="S192" s="3" t="inlineStr">
@@ -21773,9 +21771,7 @@
           <t>Berlin School District/SAU 3</t>
         </is>
       </c>
-      <c r="V192" s="3" t="n">
-        <v>-5</v>
-      </c>
+      <c r="V192" s="3" t="n"/>
       <c r="W192" s="3" t="n"/>
       <c r="X192" s="3">
         <f>IF(Y192=TRUE,"",IF(ISNUMBER(W192),W192,V192))</f>
@@ -21851,12 +21847,12 @@
       <c r="N193" t="inlineStr"/>
       <c r="O193" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>153</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>71</t>
         </is>
       </c>
       <c r="Q193" s="2" t="inlineStr">
@@ -22021,12 +22017,12 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Awaiting Response</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>processed</t>
+          <t>done</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -22067,20 +22063,20 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>2026-04-02 05:03</t>
-        </is>
-      </c>
-      <c r="N195" t="inlineStr"/>
+          <t>2026-05-20 20:02</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>2026-05-20 20:02</t>
+        </is>
+      </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="P195" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr"/>
       <c r="Q195" s="2" t="inlineStr">
         <is>
           <t>https://www.muckrock.com/foi/concord-3844/pd-chief-performance-evaluation-concord-police-department-199801/</t>
@@ -22088,7 +22084,7 @@
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>transparent-nh</t>
+          <t>transparent-nh, nh-inperson</t>
         </is>
       </c>
       <c r="S195" s="3" t="inlineStr">
@@ -22107,7 +22103,7 @@
         </is>
       </c>
       <c r="V195" s="3" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="W195" s="3" t="n"/>
       <c r="X195" s="3">
@@ -22243,12 +22239,12 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>done</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -22279,7 +22275,7 @@
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.04</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -22289,17 +22285,17 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>2026-01-29 14:40</t>
+          <t>2026-05-22 17:03</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>2026-01-29 14:40</t>
+          <t>2026-05-22 17:03</t>
         </is>
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>116</t>
         </is>
       </c>
       <c r="P197" t="inlineStr"/>
@@ -22310,7 +22306,7 @@
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>transparent-nh</t>
+          <t>transparent-nh, nh-inperson, nh-pickedup</t>
         </is>
       </c>
       <c r="S197" s="3" t="inlineStr">
@@ -22329,7 +22325,7 @@
         </is>
       </c>
       <c r="V197" s="3" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
       <c r="W197" s="3" t="n"/>
       <c r="X197" s="3">
@@ -23246,12 +23242,12 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Awaiting Response</t>
+          <t>Partially Completed</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>processed</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -23292,18 +23288,18 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>2026-02-25 14:31</t>
+          <t>2026-06-04 18:27</t>
         </is>
       </c>
       <c r="N206" t="inlineStr"/>
       <c r="O206" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>153</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q206" s="2" t="inlineStr">
@@ -23331,9 +23327,7 @@
           <t>Contoocook Valley School District/SAU1</t>
         </is>
       </c>
-      <c r="V206" s="3" t="n">
-        <v>-3</v>
-      </c>
+      <c r="V206" s="3" t="n"/>
       <c r="W206" s="3" t="n"/>
       <c r="X206" s="3">
         <f>IF(Y206=TRUE,"",IF(ISNUMBER(W206),W206,V206))</f>
@@ -23424,7 +23418,7 @@
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>transparent-nh, nh-citizen, nh-inperson</t>
+          <t>transparent-nh, nh-citizen</t>
         </is>
       </c>
       <c r="S207" s="3" t="inlineStr">
@@ -23535,7 +23529,7 @@
       </c>
       <c r="R208" t="inlineStr">
         <is>
-          <t>transparent-nh</t>
+          <t>transparent-nh, nh-privacy</t>
         </is>
       </c>
       <c r="S208" s="3" t="inlineStr">
@@ -23554,7 +23548,7 @@
         </is>
       </c>
       <c r="V208" s="3" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="W208" s="3" t="n"/>
       <c r="X208" s="3">
@@ -23690,12 +23684,12 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Awaiting Acknowledgement</t>
+          <t>Partially Completed</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>ack</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -23736,20 +23730,20 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>2026-05-15 12:34</t>
-        </is>
-      </c>
-      <c r="N210" t="inlineStr"/>
+          <t>2026-06-15 13:18</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>2026-06-15 13:18</t>
+        </is>
+      </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P210" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr"/>
       <c r="Q210" s="2" t="inlineStr">
         <is>
           <t>https://www.muckrock.com/foi/lebanon-3917/pd-settlement-agreements-211336/</t>
@@ -23757,7 +23751,7 @@
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>transparent-nh</t>
+          <t>transparent-nh, nh-inperson</t>
         </is>
       </c>
       <c r="S210" s="3" t="inlineStr">
@@ -24354,12 +24348,12 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Awaiting Acknowledgement</t>
+          <t>Partially Completed</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>ack</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -24400,18 +24394,18 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>2026-05-12 17:19</t>
+          <t>2026-05-15 18:25</t>
         </is>
       </c>
       <c r="N216" t="inlineStr"/>
       <c r="O216" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>130</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>43</t>
         </is>
       </c>
       <c r="Q216" s="2" t="inlineStr">
@@ -24421,7 +24415,7 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>transparent-nh</t>
+          <t>transparent-nh, nh-inperson</t>
         </is>
       </c>
       <c r="S216" s="3" t="inlineStr">
@@ -24439,9 +24433,7 @@
           <t>Berlin School District/SAU 3</t>
         </is>
       </c>
-      <c r="V216" s="3" t="n">
-        <v>-5</v>
-      </c>
+      <c r="V216" s="3" t="n"/>
       <c r="W216" s="3" t="n"/>
       <c r="X216" s="3">
         <f>IF(Y216=TRUE,"",IF(ISNUMBER(W216),W216,V216))</f>
@@ -24622,18 +24614,18 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>2026-01-15 16:05</t>
+          <t>2026-05-29 17:35</t>
         </is>
       </c>
       <c r="N218" t="inlineStr"/>
       <c r="O218" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>130</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>33</t>
         </is>
       </c>
       <c r="Q218" s="2" t="inlineStr">
@@ -25024,12 +25016,12 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Consolidated</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -25109,9 +25101,7 @@
           <t>Laconia School District/SAU30</t>
         </is>
       </c>
-      <c r="V222" s="3" t="n">
-        <v>-4</v>
-      </c>
+      <c r="V222" s="3" t="n"/>
       <c r="W222" s="3" t="n"/>
       <c r="X222" s="3">
         <f>IF(Y222=TRUE,"",IF(ISNUMBER(W222),W222,V222))</f>
@@ -25135,12 +25125,12 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Awaiting Response</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>processed</t>
+          <t>done</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -25168,7 +25158,11 @@
           <t>23852</t>
         </is>
       </c>
-      <c r="J223" t="inlineStr"/>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>26-31</t>
+        </is>
+      </c>
       <c r="K223" t="inlineStr">
         <is>
           <t>0</t>
@@ -25181,20 +25175,20 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>2026-04-07 05:00</t>
-        </is>
-      </c>
-      <c r="N223" t="inlineStr"/>
+          <t>2026-06-02 17:32</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>2026-06-02 17:32</t>
+        </is>
+      </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="P223" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr"/>
       <c r="Q223" s="2" t="inlineStr">
         <is>
           <t>https://www.muckrock.com/foi/nashua-3944/pd-settlement-agreements-202350/</t>
@@ -25221,7 +25215,7 @@
         </is>
       </c>
       <c r="V223" s="3" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="W223" s="3" t="n"/>
       <c r="X223" s="3">
@@ -25246,12 +25240,12 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Partially Completed</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -25331,9 +25325,7 @@
           <t>Rochester School District/SAU54</t>
         </is>
       </c>
-      <c r="V224" s="3" t="n">
-        <v>-4</v>
-      </c>
+      <c r="V224" s="3" t="n"/>
       <c r="W224" s="3" t="n"/>
       <c r="X224" s="3">
         <f>IF(Y224=TRUE,"",IF(ISNUMBER(W224),W224,V224))</f>
@@ -25690,12 +25682,12 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Awaiting Response</t>
+          <t>No Responsive Documents</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>processed</t>
+          <t>no_docs</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -25739,17 +25731,17 @@
           <t>2026-05-14 16:32</t>
         </is>
       </c>
-      <c r="N228" t="inlineStr"/>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>2026-05-14 16:32</t>
+        </is>
+      </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="P228" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr"/>
       <c r="Q228" s="2" t="inlineStr">
         <is>
           <t>https://www.muckrock.com/foi/bow-3822/pd-settlement-agreements-202356/</t>
@@ -25776,7 +25768,7 @@
         </is>
       </c>
       <c r="V228" s="3" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="W228" s="3" t="n"/>
       <c r="X228" s="3">
@@ -26023,12 +26015,12 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Partially Completed</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -26090,7 +26082,7 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>transparent-nh</t>
+          <t>transparent-nh, inperson</t>
         </is>
       </c>
       <c r="S231" s="3" t="inlineStr">
@@ -26108,9 +26100,7 @@
           <t>Oyster River Cooperative School District/SAU5</t>
         </is>
       </c>
-      <c r="V231" s="3" t="n">
-        <v>5</v>
-      </c>
+      <c r="V231" s="3" t="n"/>
       <c r="W231" s="3" t="n"/>
       <c r="X231" s="3">
         <f>IF(Y231=TRUE,"",IF(ISNUMBER(W231),W231,V231))</f>
@@ -26134,12 +26124,12 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Awaiting Response</t>
+          <t>Partially Completed</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>processed</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -26190,12 +26180,12 @@
       <c r="N232" t="inlineStr"/>
       <c r="O232" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>130</t>
         </is>
       </c>
       <c r="P232" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>57</t>
         </is>
       </c>
       <c r="Q232" s="2" t="inlineStr">
@@ -26223,9 +26213,7 @@
           <t>Portsmouth School District/SAU52</t>
         </is>
       </c>
-      <c r="V232" s="3" t="n">
-        <v>-3</v>
-      </c>
+      <c r="V232" s="3" t="n"/>
       <c r="W232" s="3" t="n"/>
       <c r="X232" s="3">
         <f>IF(Y232=TRUE,"",IF(ISNUMBER(W232),W232,V232))</f>
@@ -26295,20 +26283,20 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>2026-05-15 19:34</t>
+          <t>2026-07-13 05:01</t>
         </is>
       </c>
       <c r="N233" t="inlineStr"/>
       <c r="O233" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="P233" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="Q233" s="2" t="inlineStr">
         <is>
           <t>https://www.muckrock.com/foi/troy-4012/pd-settlement-agreements-211356/</t>
@@ -26334,7 +26322,9 @@
           <t>Monadnock Regional School District/SAU93</t>
         </is>
       </c>
-      <c r="V233" s="3" t="n"/>
+      <c r="V233" s="3" t="n">
+        <v>-5</v>
+      </c>
       <c r="W233" s="3" t="n"/>
       <c r="X233" s="3">
         <f>IF(Y233=TRUE,"",IF(ISNUMBER(W233),W233,V233))</f>
@@ -26358,12 +26348,12 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Processing</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>done</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -26391,7 +26381,11 @@
           <t>23852</t>
         </is>
       </c>
-      <c r="J234" t="inlineStr"/>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>26-372</t>
+        </is>
+      </c>
       <c r="K234" t="inlineStr">
         <is>
           <t>0</t>
@@ -26404,20 +26398,20 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>2026-05-15 14:44</t>
-        </is>
-      </c>
-      <c r="N234" t="inlineStr"/>
+          <t>2026-05-28 17:21</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>2026-05-28 17:21</t>
+        </is>
+      </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P234" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr"/>
       <c r="Q234" s="2" t="inlineStr">
         <is>
           <t>https://www.muckrock.com/foi/nashua-3944/pd-settlement-agreements-211343/</t>
@@ -26425,7 +26419,7 @@
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>transparent-nh</t>
+          <t>transparent-nh, nh-inperson</t>
         </is>
       </c>
       <c r="S234" s="3" t="inlineStr">
@@ -26443,7 +26437,9 @@
           <t>Nashua School District/SAU 42</t>
         </is>
       </c>
-      <c r="V234" s="3" t="n"/>
+      <c r="V234" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="W234" s="3" t="n"/>
       <c r="X234" s="3">
         <f>IF(Y234=TRUE,"",IF(ISNUMBER(W234),W234,V234))</f>
@@ -26467,12 +26463,12 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Processing</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -26513,20 +26509,20 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>2026-05-15 19:32</t>
-        </is>
-      </c>
-      <c r="N235" t="inlineStr"/>
+          <t>2026-05-21 18:26</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>2026-05-21 18:26</t>
+        </is>
+      </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P235" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P235" t="inlineStr"/>
       <c r="Q235" s="2" t="inlineStr">
         <is>
           <t>https://www.muckrock.com/foi/troy-4012/performance-evaluation-211355/</t>
@@ -26552,7 +26548,9 @@
           <t>Monadnock Regional School District/SAU93</t>
         </is>
       </c>
-      <c r="V235" s="3" t="n"/>
+      <c r="V235" s="3" t="n">
+        <v>-4</v>
+      </c>
       <c r="W235" s="3" t="n"/>
       <c r="X235" s="3">
         <f>IF(Y235=TRUE,"",IF(ISNUMBER(W235),W235,V235))</f>
@@ -26576,12 +26574,12 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Processing</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>submitted</t>
+          <t>done</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -26622,20 +26620,20 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>2026-05-14 21:37</t>
-        </is>
-      </c>
-      <c r="N236" t="inlineStr"/>
+          <t>2026-05-15 16:11</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>2026-05-15 16:11</t>
+        </is>
+      </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="P236" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P236" t="inlineStr"/>
       <c r="Q236" s="2" t="inlineStr">
         <is>
           <t>https://www.muckrock.com/foi/durham-3859/performance-evaluation-211281/</t>
@@ -26661,7 +26659,9 @@
           <t>Oyster River Cooperative School District/SAU5</t>
         </is>
       </c>
-      <c r="V236" s="3" t="n"/>
+      <c r="V236" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="W236" s="3" t="n"/>
       <c r="X236" s="3">
         <f>IF(Y236=TRUE,"",IF(ISNUMBER(W236),W236,V236))</f>
@@ -26959,12 +26959,12 @@
       <c r="N239" t="inlineStr"/>
       <c r="O239" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>84</t>
         </is>
       </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>79</t>
         </is>
       </c>
       <c r="Q239" s="2" t="inlineStr">
@@ -27016,12 +27016,12 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Awaiting Response</t>
+          <t>Partially Completed</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>processed</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -27062,17 +27062,17 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>2026-04-14 12:08</t>
+          <t>2026-06-03 17:23</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
         <is>
-          <t>2026-03-26 16:56</t>
+          <t>2026-05-18 18:08</t>
         </is>
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>43</t>
         </is>
       </c>
       <c r="P240" t="inlineStr"/>
@@ -27083,7 +27083,7 @@
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>transparent-nh</t>
+          <t>transparent-nh, nh-inperson</t>
         </is>
       </c>
       <c r="S240" s="3" t="inlineStr">
@@ -27288,12 +27288,12 @@
       <c r="N242" t="inlineStr"/>
       <c r="O242" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>84</t>
         </is>
       </c>
       <c r="P242" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>68</t>
         </is>
       </c>
       <c r="Q242" s="2" t="inlineStr">
@@ -27847,12 +27847,12 @@
       <c r="N247" t="inlineStr"/>
       <c r="O247" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>84</t>
         </is>
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>47</t>
         </is>
       </c>
       <c r="Q247" s="2" t="inlineStr">
@@ -28128,12 +28128,12 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Awaiting Acknowledgement</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>ack</t>
+          <t>done</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -28177,17 +28177,17 @@
           <t>2026-04-10 05:01</t>
         </is>
       </c>
-      <c r="N250" t="inlineStr"/>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>2026-04-10 05:01</t>
+        </is>
+      </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="P250" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="P250" t="inlineStr"/>
       <c r="Q250" s="2" t="inlineStr">
         <is>
           <t>https://www.muckrock.com/foi/dover-3855/performance-evaluation-dover-school-districtsau11-207114/</t>
@@ -28214,7 +28214,7 @@
         </is>
       </c>
       <c r="V250" s="3" t="n">
-        <v>-5</v>
+        <v>4</v>
       </c>
       <c r="W250" s="3" t="n"/>
       <c r="X250" s="3">
@@ -28683,12 +28683,12 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>No Responsive Documents</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>no_docs</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -28769,7 +28769,7 @@
         </is>
       </c>
       <c r="V255" s="3" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="W255" s="3" t="n"/>
       <c r="X255" s="3">
@@ -28957,12 +28957,12 @@
       <c r="N257" t="inlineStr"/>
       <c r="O257" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>84</t>
         </is>
       </c>
       <c r="P257" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>68</t>
         </is>
       </c>
       <c r="Q257" s="2" t="inlineStr">
@@ -30075,12 +30075,12 @@
       <c r="N267" t="inlineStr"/>
       <c r="O267" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>84</t>
         </is>
       </c>
       <c r="P267" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>81</t>
         </is>
       </c>
       <c r="Q267" s="2" t="inlineStr">
@@ -30090,7 +30090,7 @@
       </c>
       <c r="R267" t="inlineStr">
         <is>
-          <t>transparent-nh</t>
+          <t>transparent-nh, nh-inperson</t>
         </is>
       </c>
       <c r="S267" s="3" t="inlineStr">
@@ -30132,12 +30132,12 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Awaiting Acknowledgement</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>ack</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -30181,17 +30181,17 @@
           <t>2026-03-19 15:47</t>
         </is>
       </c>
-      <c r="N268" t="inlineStr"/>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>2026-03-19 15:47</t>
+        </is>
+      </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="P268" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P268" t="inlineStr"/>
       <c r="Q268" s="2" t="inlineStr">
         <is>
           <t>https://www.muckrock.com/foi/portsmouth-3975/performance-evaluation-portsmouth-clerk-207089/</t>
@@ -30218,7 +30218,7 @@
         </is>
       </c>
       <c r="V268" s="3" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="W268" s="3" t="n"/>
       <c r="X268" s="3">
@@ -30243,12 +30243,12 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Awaiting Acknowledgement</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>ack</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -30292,17 +30292,17 @@
           <t>2026-04-10 05:01</t>
         </is>
       </c>
-      <c r="N269" t="inlineStr"/>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>2026-04-10 05:01</t>
+        </is>
+      </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="P269" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="P269" t="inlineStr"/>
       <c r="Q269" s="2" t="inlineStr">
         <is>
           <t>https://www.muckrock.com/foi/new-hampshire-81/performance-evaluation-portsmouth-school-district-207099/</t>
@@ -30329,7 +30329,7 @@
         </is>
       </c>
       <c r="V269" s="3" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="W269" s="3" t="n"/>
       <c r="X269" s="3">
@@ -30687,12 +30687,12 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Awaiting Acknowledgement</t>
+          <t>Awaiting Response</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>ack</t>
+          <t>processed</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -30733,18 +30733,18 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>2026-04-10 05:01</t>
+          <t>2026-06-01 11:52</t>
         </is>
       </c>
       <c r="N273" t="inlineStr"/>
       <c r="O273" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>84</t>
         </is>
       </c>
       <c r="P273" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>32</t>
         </is>
       </c>
       <c r="Q273" s="2" t="inlineStr">
@@ -30773,7 +30773,7 @@
         </is>
       </c>
       <c r="V273" s="3" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="W273" s="3" t="n"/>
       <c r="X273" s="3">
@@ -30850,12 +30850,12 @@
       <c r="N274" t="inlineStr"/>
       <c r="O274" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>84</t>
         </is>
       </c>
       <c r="P274" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>68</t>
         </is>
       </c>
       <c r="Q274" s="2" t="inlineStr">
@@ -30909,12 +30909,12 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Awaiting Acknowledgement</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>ack</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -30955,20 +30955,20 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>2026-04-10 05:01</t>
-        </is>
-      </c>
-      <c r="N275" t="inlineStr"/>
+          <t>2026-05-29 12:42</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>2026-05-29 12:42</t>
+        </is>
+      </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="P275" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="P275" t="inlineStr"/>
       <c r="Q275" s="2" t="inlineStr">
         <is>
           <t>https://www.muckrock.com/foi/new-hampshire-81/performance-evaluation-sau67-207095/</t>
@@ -30995,7 +30995,7 @@
         </is>
       </c>
       <c r="V275" s="3" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="W275" s="3" t="n"/>
       <c r="X275" s="3">
@@ -31294,12 +31294,12 @@
       <c r="N278" t="inlineStr"/>
       <c r="O278" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>84</t>
         </is>
       </c>
       <c r="P278" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>82</t>
         </is>
       </c>
       <c r="Q278" s="2" t="inlineStr">
@@ -31462,12 +31462,12 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Awaiting Response</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>processed</t>
+          <t>done</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -31508,20 +31508,20 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>2026-04-11 11:08</t>
-        </is>
-      </c>
-      <c r="N280" t="inlineStr"/>
+          <t>2026-07-08 13:49</t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>2026-07-08 13:49</t>
+        </is>
+      </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="P280" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="P280" t="inlineStr"/>
       <c r="Q280" s="2" t="inlineStr">
         <is>
           <t>https://www.muckrock.com/foi/somersworth-3993/performance-evaluation-somersworth-school-districtsau56-207111/</t>
@@ -31548,7 +31548,7 @@
         </is>
       </c>
       <c r="V280" s="3" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="W280" s="3" t="n"/>
       <c r="X280" s="3">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Awaiting Acknowledgement</t>
+          <t>Partially Completed</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>ack</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -31619,20 +31619,20 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>2026-05-15 18:58</t>
-        </is>
-      </c>
-      <c r="N281" t="inlineStr"/>
+          <t>2026-05-15 19:43</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>2026-05-15 19:43</t>
+        </is>
+      </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P281" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P281" t="inlineStr"/>
       <c r="Q281" s="2" t="inlineStr">
         <is>
           <t>https://www.muckrock.com/foi/concord-3844/rfp-list-211349/</t>
@@ -31640,7 +31640,7 @@
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>transparent-nh</t>
+          <t>transparent-nh, nh-inperson</t>
         </is>
       </c>
       <c r="S281" s="3" t="inlineStr">

--- a/scorecard.xlsx
+++ b/scorecard.xlsx
@@ -967,18 +967,18 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-06-30 05:00</t>
+          <t>2026-07-15 05:00</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>150</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1643,12 +1643,12 @@
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3520,18 +3520,18 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-06-30 05:00</t>
+          <t>2026-07-15 05:00</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>150</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>150</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>89</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5425,12 +5425,12 @@
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>150</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>120</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6085,12 +6085,12 @@
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>132</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>99</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>154</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>transparent-nh, nh-inperson</t>
+          <t>transparent-nh, nh-inperson, nh-rfp</t>
         </is>
       </c>
       <c r="S71" s="3" t="inlineStr">
@@ -8351,7 +8351,7 @@
         <v/>
       </c>
       <c r="Y71" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z71" s="3" t="n"/>
     </row>
@@ -8435,7 +8435,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>transparent-nh, nh-inperson</t>
+          <t>transparent-nh, nh-inperson, nh-rfp</t>
         </is>
       </c>
       <c r="S72" s="3" t="inlineStr">
@@ -8462,7 +8462,7 @@
         <v/>
       </c>
       <c r="Y72" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z72" s="3" t="n"/>
     </row>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>transparent-nh</t>
+          <t>transparent-nh, nh-rfp</t>
         </is>
       </c>
       <c r="S73" s="3" t="inlineStr">
@@ -8573,7 +8573,7 @@
         <v/>
       </c>
       <c r="Y73" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z73" s="3" t="n"/>
     </row>
@@ -8657,7 +8657,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>transparent-nh</t>
+          <t>transparent-nh, nh-rfp</t>
         </is>
       </c>
       <c r="S74" s="3" t="inlineStr">
@@ -8684,7 +8684,7 @@
         <v/>
       </c>
       <c r="Y74" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z74" s="3" t="n"/>
     </row>
@@ -8753,12 +8753,12 @@
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>147</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>transparent-nh</t>
+          <t>transparent-nh, nh-rfp</t>
         </is>
       </c>
       <c r="S75" s="3" t="inlineStr">
@@ -8795,7 +8795,7 @@
         <v/>
       </c>
       <c r="Y75" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z75" s="3" t="n"/>
     </row>
@@ -8868,12 +8868,12 @@
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>147</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -8883,7 +8883,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>transparent-nh</t>
+          <t>transparent-nh, nh-rfp</t>
         </is>
       </c>
       <c r="S76" s="3" t="inlineStr">
@@ -8910,7 +8910,7 @@
         <v/>
       </c>
       <c r="Y76" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z76" s="3" t="n"/>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>transparent-nh, nh-citizen</t>
+          <t>transparent-nh, nh-citizen, nh-rfp</t>
         </is>
       </c>
       <c r="S77" s="3" t="inlineStr">
@@ -9019,7 +9019,7 @@
         <v/>
       </c>
       <c r="Y77" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z77" s="3" t="n"/>
     </row>
@@ -9103,7 +9103,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>transparent-nh, nh-citizen</t>
+          <t>transparent-nh, nh-citizen, nh-rfp</t>
         </is>
       </c>
       <c r="S78" s="3" t="inlineStr">
@@ -9130,7 +9130,7 @@
         <v/>
       </c>
       <c r="Y78" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z78" s="3" t="n"/>
     </row>
@@ -9214,7 +9214,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>transparent-nh</t>
+          <t>transparent-nh, nh-rfp</t>
         </is>
       </c>
       <c r="S79" s="3" t="inlineStr">
@@ -9241,7 +9241,7 @@
         <v/>
       </c>
       <c r="Y79" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z79" s="3" t="n"/>
     </row>
@@ -9310,12 +9310,12 @@
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9325,7 +9325,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>transparent-nh</t>
+          <t>transparent-nh, nh-rfp</t>
         </is>
       </c>
       <c r="S80" s="3" t="inlineStr">
@@ -9434,7 +9434,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>transparent-nh</t>
+          <t>transparent-nh, nh-rfp</t>
         </is>
       </c>
       <c r="S81" s="3" t="inlineStr">
@@ -9461,7 +9461,7 @@
         <v/>
       </c>
       <c r="Y81" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z81" s="3" t="n"/>
     </row>
@@ -9545,7 +9545,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>transparent-nh, nh-citizen</t>
+          <t>transparent-nh, nh-citizen, nh-rfp</t>
         </is>
       </c>
       <c r="S82" s="3" t="inlineStr">
@@ -9572,7 +9572,7 @@
         <v/>
       </c>
       <c r="Y82" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z82" s="3" t="n"/>
     </row>
@@ -9656,7 +9656,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>transparent-nh, nh-inperson</t>
+          <t>transparent-nh, nh-inperson, nh-rfp</t>
         </is>
       </c>
       <c r="S83" s="3" t="inlineStr">
@@ -9681,7 +9681,7 @@
         <v/>
       </c>
       <c r="Y83" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z83" s="3" t="n"/>
     </row>
@@ -9765,7 +9765,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>transparent-nh, nh-inperson, nh-pickedup</t>
+          <t>transparent-nh, nh-inperson, nh-pickedup, nh-rfp</t>
         </is>
       </c>
       <c r="S84" s="3" t="inlineStr">
@@ -9792,7 +9792,7 @@
         <v/>
       </c>
       <c r="Y84" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z84" s="3" t="n"/>
     </row>
@@ -9876,7 +9876,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>transparent-nh, nh-inperson</t>
+          <t>transparent-nh, nh-inperson, nh-rfp</t>
         </is>
       </c>
       <c r="S85" s="3" t="inlineStr">
@@ -9901,7 +9901,7 @@
         <v/>
       </c>
       <c r="Y85" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z85" s="3" t="n"/>
     </row>
@@ -9974,12 +9974,12 @@
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>147</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -9989,7 +9989,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>transparent-nh</t>
+          <t>transparent-nh, nh-rfp</t>
         </is>
       </c>
       <c r="S86" s="3" t="inlineStr">
@@ -10083,12 +10083,12 @@
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>147</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>137</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -10098,7 +10098,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>transparent-nh, nh-inperson</t>
+          <t>transparent-nh, nh-inperson, nh-rfp</t>
         </is>
       </c>
       <c r="S87" s="3" t="inlineStr">
@@ -10123,7 +10123,7 @@
         <v/>
       </c>
       <c r="Y87" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z87" s="3" t="n"/>
     </row>
@@ -10207,7 +10207,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>transparent-nh, nh-inperson</t>
+          <t>transparent-nh, nh-inperson, nh-rfp</t>
         </is>
       </c>
       <c r="S88" s="3" t="inlineStr">
@@ -10234,7 +10234,7 @@
         <v/>
       </c>
       <c r="Y88" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z88" s="3" t="n"/>
     </row>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>transparent-nh, nh-citizen, nh-inperson</t>
+          <t>transparent-nh, nh-citizen, nh-inperson, nh-rfp</t>
         </is>
       </c>
       <c r="S89" s="3" t="inlineStr">
@@ -10345,7 +10345,7 @@
         <v/>
       </c>
       <c r="Y89" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z89" s="3" t="n"/>
     </row>
@@ -10429,7 +10429,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>transparent-nh, nh-citizen</t>
+          <t>transparent-nh, nh-citizen, nh-rfp</t>
         </is>
       </c>
       <c r="S90" s="3" t="inlineStr">
@@ -10456,7 +10456,7 @@
         <v/>
       </c>
       <c r="Y90" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z90" s="3" t="n"/>
     </row>
@@ -10525,12 +10525,12 @@
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>147</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>120</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -10540,7 +10540,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>transparent-nh, nh-inperson</t>
+          <t>transparent-nh, nh-inperson, nh-rfp</t>
         </is>
       </c>
       <c r="S91" s="3" t="inlineStr">
@@ -10565,7 +10565,7 @@
         <v/>
       </c>
       <c r="Y91" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z91" s="3" t="n"/>
     </row>
@@ -10634,12 +10634,12 @@
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>42</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>transparent-nh</t>
+          <t>transparent-nh, nh-rfp</t>
         </is>
       </c>
       <c r="S92" s="3" t="inlineStr">
@@ -10676,7 +10676,7 @@
         <v/>
       </c>
       <c r="Y92" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z92" s="3" t="n"/>
     </row>
@@ -10758,7 +10758,11 @@
           <t>https://www.muckrock.com/foi/troy-4012/highest-value-rfps-troy-clerk-200680/</t>
         </is>
       </c>
-      <c r="R93" t="inlineStr"/>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>nh-rfp</t>
+        </is>
+      </c>
       <c r="S93" s="3" t="inlineStr">
         <is>
           <t>Troy</t>
@@ -10783,7 +10787,7 @@
         <v/>
       </c>
       <c r="Y93" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z93" s="3" t="n"/>
     </row>
@@ -10963,12 +10967,12 @@
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -11074,12 +11078,12 @@
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>83</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -11294,12 +11298,12 @@
       <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -11623,12 +11627,12 @@
       <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>69</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -12178,12 +12182,12 @@
       <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>48</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -12289,12 +12293,12 @@
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -12400,12 +12404,12 @@
       <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>70</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -12842,12 +12846,12 @@
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -13288,12 +13292,12 @@
       <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>69</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -13843,12 +13847,12 @@
       <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -14404,12 +14408,12 @@
       <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -14513,12 +14517,12 @@
       <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>69</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -14622,12 +14626,12 @@
       <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>69</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
@@ -15173,12 +15177,12 @@
       <c r="N133" t="inlineStr"/>
       <c r="O133" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>69</t>
         </is>
       </c>
       <c r="Q133" s="2" t="inlineStr">
@@ -15284,12 +15288,12 @@
       <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Q134" s="2" t="inlineStr">
@@ -15395,12 +15399,12 @@
       <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -15617,12 +15621,12 @@
       <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>83</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
@@ -15835,12 +15839,12 @@
       <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
@@ -17837,12 +17841,12 @@
       <c r="N157" t="inlineStr"/>
       <c r="O157" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>114</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -19284,12 +19288,12 @@
       <c r="N170" t="inlineStr"/>
       <c r="O170" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>116</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -20402,12 +20406,12 @@
       <c r="N180" t="inlineStr"/>
       <c r="O180" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>116</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -21516,12 +21520,12 @@
       <c r="N190" t="inlineStr"/>
       <c r="O190" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
@@ -21738,12 +21742,12 @@
       <c r="N192" t="inlineStr"/>
       <c r="O192" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>154</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="Q192" s="2" t="inlineStr">
@@ -21847,12 +21851,12 @@
       <c r="N193" t="inlineStr"/>
       <c r="O193" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>154</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="Q193" s="2" t="inlineStr">
@@ -23294,12 +23298,12 @@
       <c r="N206" t="inlineStr"/>
       <c r="O206" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>154</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q206" s="2" t="inlineStr">
@@ -24400,12 +24404,12 @@
       <c r="N216" t="inlineStr"/>
       <c r="O216" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>131</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="Q216" s="2" t="inlineStr">
@@ -24620,12 +24624,12 @@
       <c r="N218" t="inlineStr"/>
       <c r="O218" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>131</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Q218" s="2" t="inlineStr">
@@ -26180,12 +26184,12 @@
       <c r="N232" t="inlineStr"/>
       <c r="O232" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>131</t>
         </is>
       </c>
       <c r="P232" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>58</t>
         </is>
       </c>
       <c r="Q232" s="2" t="inlineStr">
@@ -26289,12 +26293,12 @@
       <c r="N233" t="inlineStr"/>
       <c r="O233" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q233" s="2" t="inlineStr">
@@ -26959,12 +26963,12 @@
       <c r="N239" t="inlineStr"/>
       <c r="O239" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>80</t>
         </is>
       </c>
       <c r="Q239" s="2" t="inlineStr">
@@ -27288,12 +27292,12 @@
       <c r="N242" t="inlineStr"/>
       <c r="O242" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="P242" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>69</t>
         </is>
       </c>
       <c r="Q242" s="2" t="inlineStr">
@@ -27847,12 +27851,12 @@
       <c r="N247" t="inlineStr"/>
       <c r="O247" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>48</t>
         </is>
       </c>
       <c r="Q247" s="2" t="inlineStr">
@@ -28957,12 +28961,12 @@
       <c r="N257" t="inlineStr"/>
       <c r="O257" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="P257" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>69</t>
         </is>
       </c>
       <c r="Q257" s="2" t="inlineStr">
@@ -30075,12 +30079,12 @@
       <c r="N267" t="inlineStr"/>
       <c r="O267" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="P267" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>82</t>
         </is>
       </c>
       <c r="Q267" s="2" t="inlineStr">
@@ -30739,12 +30743,12 @@
       <c r="N273" t="inlineStr"/>
       <c r="O273" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="P273" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="Q273" s="2" t="inlineStr">
@@ -30850,12 +30854,12 @@
       <c r="N274" t="inlineStr"/>
       <c r="O274" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="P274" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>69</t>
         </is>
       </c>
       <c r="Q274" s="2" t="inlineStr">
@@ -31294,12 +31298,12 @@
       <c r="N278" t="inlineStr"/>
       <c r="O278" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="P278" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>83</t>
         </is>
       </c>
       <c r="Q278" s="2" t="inlineStr">
@@ -31640,7 +31644,7 @@
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>transparent-nh, nh-inperson</t>
+          <t>transparent-nh, nh-inperson, nh-rfp</t>
         </is>
       </c>
       <c r="S281" s="3" t="inlineStr">

--- a/scorecard.xlsx
+++ b/scorecard.xlsx
@@ -973,12 +973,12 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>153</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1643,12 +1643,12 @@
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>47</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>153</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>153</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5425,12 +5425,12 @@
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>153</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>123</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6085,12 +6085,12 @@
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>135</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>102</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Awaiting Response</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>processed</t>
+          <t>done</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -6743,17 +6743,17 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-07-01 05:00</t>
+          <t>2026-07-16 15:02</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>2026-01-16 17:17</t>
+          <t>2026-07-16 15:02</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>133</t>
         </is>
       </c>
       <c r="P57" t="inlineStr"/>
@@ -6782,7 +6782,9 @@
           <t>Interstate School District/SAU70</t>
         </is>
       </c>
-      <c r="V57" s="3" t="n"/>
+      <c r="V57" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="W57" s="3" t="n"/>
       <c r="X57" s="3">
         <f>IF(Y57=TRUE,"",IF(ISNUMBER(W57),W57,V57))</f>
@@ -7528,12 +7530,12 @@
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>157</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8747,18 +8749,18 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2026-07-03 05:03</t>
+          <t>2026-07-20 05:02</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>150</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -8868,12 +8870,12 @@
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>150</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9310,12 +9312,12 @@
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>48</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9974,12 +9976,12 @@
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>150</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>44</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10083,12 +10085,12 @@
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>150</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>140</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -10525,12 +10527,12 @@
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>150</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>123</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -10628,18 +10630,18 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2026-05-19 22:45</t>
+          <t>2026-07-20 05:02</t>
         </is>
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>48</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -10915,12 +10917,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Awaiting Response</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>processed</t>
+          <t>done</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -10961,20 +10963,20 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>2026-07-01 13:25</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
+          <t>2026-07-20 13:38</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>2026-07-20 13:38</t>
+        </is>
+      </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr"/>
       <c r="Q95" s="2" t="inlineStr">
         <is>
           <t>https://www.muckrock.com/foi/troy-4012/leadership-and-constituent-emails-211354/</t>
@@ -11001,7 +11003,7 @@
         </is>
       </c>
       <c r="V95" s="3" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="W95" s="3" t="n"/>
       <c r="X95" s="3">
@@ -11078,12 +11080,12 @@
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>88</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>86</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -11298,12 +11300,12 @@
       <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>88</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>76</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -11627,12 +11629,12 @@
       <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>88</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>72</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -12182,12 +12184,12 @@
       <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>88</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>51</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -12293,12 +12295,12 @@
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>88</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -12404,12 +12406,12 @@
       <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>88</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>73</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -12840,18 +12842,18 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>2026-07-01 05:00</t>
+          <t>2026-07-16 05:00</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>88</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -13292,12 +13294,12 @@
       <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>88</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>72</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -13847,12 +13849,12 @@
       <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>88</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -14408,12 +14410,12 @@
       <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>88</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>38</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -14517,12 +14519,12 @@
       <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>88</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>72</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -14626,12 +14628,12 @@
       <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>88</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>72</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
@@ -15177,12 +15179,12 @@
       <c r="N133" t="inlineStr"/>
       <c r="O133" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>88</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>72</t>
         </is>
       </c>
       <c r="Q133" s="2" t="inlineStr">
@@ -15288,12 +15290,12 @@
       <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>88</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Q134" s="2" t="inlineStr">
@@ -15399,12 +15401,12 @@
       <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>88</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>47</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -15621,12 +15623,12 @@
       <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>88</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>86</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
@@ -15839,12 +15841,12 @@
       <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>88</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>40</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
@@ -17835,18 +17837,18 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>2026-07-02 05:01</t>
+          <t>2026-07-17 05:00</t>
         </is>
       </c>
       <c r="N157" t="inlineStr"/>
       <c r="O157" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>117</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -19288,12 +19290,12 @@
       <c r="N170" t="inlineStr"/>
       <c r="O170" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>119</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>81</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -20406,12 +20408,12 @@
       <c r="N180" t="inlineStr"/>
       <c r="O180" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>119</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>81</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -21520,12 +21522,12 @@
       <c r="N190" t="inlineStr"/>
       <c r="O190" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>47</t>
         </is>
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
@@ -21742,12 +21744,12 @@
       <c r="N192" t="inlineStr"/>
       <c r="O192" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>157</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>47</t>
         </is>
       </c>
       <c r="Q192" s="2" t="inlineStr">
@@ -21851,12 +21853,12 @@
       <c r="N193" t="inlineStr"/>
       <c r="O193" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>157</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>75</t>
         </is>
       </c>
       <c r="Q193" s="2" t="inlineStr">
@@ -23298,12 +23300,12 @@
       <c r="N206" t="inlineStr"/>
       <c r="O206" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>157</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>33</t>
         </is>
       </c>
       <c r="Q206" s="2" t="inlineStr">
@@ -24404,12 +24406,12 @@
       <c r="N216" t="inlineStr"/>
       <c r="O216" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>134</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>47</t>
         </is>
       </c>
       <c r="Q216" s="2" t="inlineStr">
@@ -24624,12 +24626,12 @@
       <c r="N218" t="inlineStr"/>
       <c r="O218" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>134</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="Q218" s="2" t="inlineStr">
@@ -26184,12 +26186,12 @@
       <c r="N232" t="inlineStr"/>
       <c r="O232" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>134</t>
         </is>
       </c>
       <c r="P232" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>61</t>
         </is>
       </c>
       <c r="Q232" s="2" t="inlineStr">
@@ -26293,12 +26295,12 @@
       <c r="N233" t="inlineStr"/>
       <c r="O233" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>47</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Q233" s="2" t="inlineStr">
@@ -26963,12 +26965,12 @@
       <c r="N239" t="inlineStr"/>
       <c r="O239" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>88</t>
         </is>
       </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>83</t>
         </is>
       </c>
       <c r="Q239" s="2" t="inlineStr">
@@ -27292,12 +27294,12 @@
       <c r="N242" t="inlineStr"/>
       <c r="O242" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>88</t>
         </is>
       </c>
       <c r="P242" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>72</t>
         </is>
       </c>
       <c r="Q242" s="2" t="inlineStr">
@@ -27851,12 +27853,12 @@
       <c r="N247" t="inlineStr"/>
       <c r="O247" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>88</t>
         </is>
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>51</t>
         </is>
       </c>
       <c r="Q247" s="2" t="inlineStr">
@@ -28961,12 +28963,12 @@
       <c r="N257" t="inlineStr"/>
       <c r="O257" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>88</t>
         </is>
       </c>
       <c r="P257" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>72</t>
         </is>
       </c>
       <c r="Q257" s="2" t="inlineStr">
@@ -30079,12 +30081,12 @@
       <c r="N267" t="inlineStr"/>
       <c r="O267" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="P267" t="inlineStr">
+        <is>
           <t>85</t>
-        </is>
-      </c>
-      <c r="P267" t="inlineStr">
-        <is>
-          <t>82</t>
         </is>
       </c>
       <c r="Q267" s="2" t="inlineStr">
@@ -30743,12 +30745,12 @@
       <c r="N273" t="inlineStr"/>
       <c r="O273" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>88</t>
         </is>
       </c>
       <c r="P273" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>36</t>
         </is>
       </c>
       <c r="Q273" s="2" t="inlineStr">
@@ -30854,12 +30856,12 @@
       <c r="N274" t="inlineStr"/>
       <c r="O274" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>88</t>
         </is>
       </c>
       <c r="P274" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>72</t>
         </is>
       </c>
       <c r="Q274" s="2" t="inlineStr">
@@ -31298,12 +31300,12 @@
       <c r="N278" t="inlineStr"/>
       <c r="O278" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>88</t>
         </is>
       </c>
       <c r="P278" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>86</t>
         </is>
       </c>
       <c r="Q278" s="2" t="inlineStr">
